--- a/MainTop/12.02.2026 Таня Озон/print_print_sorted.xlsx
+++ b/MainTop/12.02.2026 Таня Озон/print_print_sorted.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\12.02.2026 Таня Озон\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\12.02.2026 Таня Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981F651E-9D40-459B-932A-5E37B649B476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549097CD-204C-4E38-AFE4-401C248489F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="95">
   <si>
     <t>Артикул</t>
   </si>
@@ -351,7 +351,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -374,11 +374,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -386,6 +399,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -688,38 +706,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="49.5703125" customWidth="1"/>
-    <col min="2" max="9" width="5.5703125" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" customWidth="1"/>
-    <col min="11" max="11" width="5.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="2" max="8" width="4.28515625" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -731,8 +751,14 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="7">
+        <v>1</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -766,8 +792,14 @@
       <c r="K2" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" s="2">
+        <v>2</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -801,8 +833,14 @@
       <c r="K3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" s="7">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -836,8 +874,14 @@
       <c r="K4" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" s="2">
+        <v>4</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -871,8 +915,14 @@
       <c r="K5" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" s="7">
+        <v>5</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
@@ -906,43 +956,49 @@
       <c r="K6" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="L6" s="2">
+        <v>6</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="3">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6">
         <v>4</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="6">
         <v>4</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="6">
         <v>7</v>
       </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3">
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
         <v>16</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
@@ -977,7 +1033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1012,7 +1068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1047,7 +1103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1082,7 +1138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1117,7 +1173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -1152,7 +1208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
@@ -1187,7 +1243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>26</v>
       </c>
@@ -1222,7 +1278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>27</v>
       </c>
